--- a/docs/pension_data_combined_2026-08-28.xlsx
+++ b/docs/pension_data_combined_2026-08-28.xlsx
@@ -1246,7 +1246,7 @@
         <v>2.1808</v>
       </c>
       <c r="D49" t="n">
-        <v>71005681.01000001</v>
+        <v>71010800.55</v>
       </c>
     </row>
     <row r="50">
@@ -1264,7 +1264,7 @@
         <v>2.1984</v>
       </c>
       <c r="D50" t="n">
-        <v>231125720.92</v>
+        <v>231138393.7</v>
       </c>
     </row>
     <row r="51">
@@ -1282,7 +1282,7 @@
         <v>2.2163</v>
       </c>
       <c r="D51" t="n">
-        <v>353969983.14</v>
+        <v>353950875.6</v>
       </c>
     </row>
     <row r="52">
@@ -1300,7 +1300,7 @@
         <v>2.2242</v>
       </c>
       <c r="D52" t="n">
-        <v>432665664.33</v>
+        <v>432715728.5</v>
       </c>
     </row>
     <row r="53">
@@ -1318,7 +1318,7 @@
         <v>1.9864</v>
       </c>
       <c r="D53" t="n">
-        <v>397933180.65</v>
+        <v>397934070.1</v>
       </c>
     </row>
     <row r="54">
@@ -1336,7 +1336,7 @@
         <v>1.5482</v>
       </c>
       <c r="D54" t="n">
-        <v>323681372.54</v>
+        <v>323451490.1</v>
       </c>
     </row>
     <row r="55">
@@ -1354,7 +1354,7 @@
         <v>1.2031</v>
       </c>
       <c r="D55" t="n">
-        <v>60139580.45</v>
+        <v>60108148.26</v>
       </c>
     </row>
   </sheetData>
